--- a/Status Track.xlsx
+++ b/Status Track.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\UI CONCEPTS\UI DEVELOPMENT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFCDCBE-80BF-4213-9B70-30FE3E2FB8F8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE94954-CBC6-4FD4-9221-682AB7EA57B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{1EAAED63-47CB-4904-984F-93FC613031AB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="58">
   <si>
     <t>Date</t>
   </si>
@@ -39,9 +39,6 @@
     <t>Done</t>
   </si>
   <si>
-    <t xml:space="preserve">Call an API and display result and Simple user form - </t>
-  </si>
-  <si>
     <t>Tech stack</t>
   </si>
   <si>
@@ -178,6 +175,30 @@
   </si>
   <si>
     <t>JS programs revision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call an API and display result and Simple user form </t>
+  </si>
+  <si>
+    <t>React programs revision</t>
+  </si>
+  <si>
+    <t>July 28 2026</t>
+  </si>
+  <si>
+    <t>July 29 2026</t>
+  </si>
+  <si>
+    <t>Javascript and HTML concepts revision</t>
+  </si>
+  <si>
+    <t>July 30 2026</t>
+  </si>
+  <si>
+    <t>React revision</t>
+  </si>
+  <si>
+    <t>July 31 2026</t>
   </si>
 </sst>
 </file>
@@ -530,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6913C840-EEDC-4502-B2DF-869A775A061E}">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -546,21 +567,21 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
@@ -568,13 +589,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
@@ -582,13 +603,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
@@ -597,18 +618,18 @@
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
@@ -616,13 +637,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
@@ -630,13 +651,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
@@ -644,13 +665,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" t="s">
         <v>3</v>
@@ -658,13 +679,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
@@ -673,18 +694,18 @@
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
         <v>25</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>27</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -692,13 +713,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
@@ -706,13 +727,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
         <v>30</v>
       </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
@@ -720,13 +741,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
         <v>32</v>
       </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" t="s">
         <v>3</v>
@@ -734,13 +755,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
         <v>34</v>
       </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
@@ -749,18 +770,18 @@
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
       </c>
       <c r="D19" t="s">
         <v>3</v>
@@ -768,13 +789,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
         <v>39</v>
-      </c>
-      <c r="C20" t="s">
-        <v>40</v>
       </c>
       <c r="D20" t="s">
         <v>3</v>
@@ -782,13 +803,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
         <v>42</v>
       </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
         <v>3</v>
@@ -796,13 +817,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" t="s">
         <v>44</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>45</v>
-      </c>
-      <c r="C22" t="s">
-        <v>46</v>
       </c>
       <c r="D22" t="s">
         <v>3</v>
@@ -810,13 +831,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" t="s">
         <v>47</v>
       </c>
-      <c r="B23" t="s">
-        <v>48</v>
-      </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" t="s">
         <v>3</v>
@@ -825,21 +846,74 @@
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
         <v>49</v>
       </c>
-      <c r="B25" t="s">
-        <v>50</v>
-      </c>
       <c r="C25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" t="s">
         <v>6</v>
       </c>
-      <c r="D25" t="s">
-        <v>3</v>
+      <c r="D26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="B30" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Status Track.xlsx
+++ b/Status Track.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\UI CONCEPTS\UI DEVELOPMENT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE94954-CBC6-4FD4-9221-682AB7EA57B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903EECEA-B3E3-48EC-8746-89B0B7522572}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{1EAAED63-47CB-4904-984F-93FC613031AB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="59">
   <si>
     <t>Date</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>July 31 2026</t>
+  </si>
+  <si>
+    <t>React prgrams : Counter and Add/remove cart using useReducer</t>
   </si>
 </sst>
 </file>
@@ -555,7 +558,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
-    <col min="2" max="2" width="48.33203125" customWidth="1"/>
+    <col min="2" max="2" width="56.88671875" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -909,6 +912,15 @@
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="B29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
